--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/OHIO_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/OHIO_2015.xlsx
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C218">
@@ -4585,7 +4585,7 @@
         <v>65</v>
       </c>
       <c r="D235">
-        <v>0.009707287933094385</v>
+        <v>0.009707287933094383</v>
       </c>
     </row>
     <row r="236">
@@ -8167,7 +8167,7 @@
         <v>64</v>
       </c>
       <c r="D434">
-        <v>0.009557945041816009</v>
+        <v>0.009557945041816007</v>
       </c>
     </row>
     <row r="435">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C599">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C600">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C634">
